--- a/GourmetProject/GameConfig/Datas/recipe.xlsx
+++ b/GourmetProject/GameConfig/Datas/recipe.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,59 +446,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>菜谱ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>固定初始菜品ID列表</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>初始要求分</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>随机菜品池条目列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>list,string</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>list,RecipeEntry</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>recipe_glutton</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>rice</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>40</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>rice,150,0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>recipe_glutton</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>rice</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>40</v>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>egg,120,0</t>
+          <t>rice,150,0</t>
         </is>
       </c>
     </row>
@@ -509,7 +525,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>soup,100,0</t>
+          <t>egg,120,0</t>
         </is>
       </c>
     </row>
@@ -520,7 +536,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>noodle,90,0</t>
+          <t>soup,100,0</t>
         </is>
       </c>
     </row>
@@ -531,39 +547,39 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>feast,40,1</t>
+          <t>noodle,90,0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>recipe_wok</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>egg</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>45</v>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>egg,120,0</t>
+          <t>feast,40,1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>recipe_wok</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>egg</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>45</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>fish,100,0</t>
+          <t>egg,120,0</t>
         </is>
       </c>
     </row>
@@ -574,7 +590,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>dumpling,90,0</t>
+          <t>fish,100,0</t>
         </is>
       </c>
     </row>
@@ -585,39 +601,39 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>cake,60,2</t>
+          <t>dumpling,90,0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>recipe_chili</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>chili</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>38</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>chili,130,0</t>
+          <t>cake,60,2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>recipe_chili</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>chili</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>38</v>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>rice,120,0</t>
+          <t>chili,130,0</t>
         </is>
       </c>
     </row>
@@ -628,7 +644,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>soup,90,0</t>
+          <t>rice,120,0</t>
         </is>
       </c>
     </row>
@@ -639,6 +655,17 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
+          <t>soup,90,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>orange,80,0</t>
         </is>
       </c>

--- a/GourmetProject/GameConfig/Datas/recipe.xlsx
+++ b/GourmetProject/GameConfig/Datas/recipe.xlsx
@@ -1,324 +1,182 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25900" windowHeight="12520"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25900" windowHeight="12520" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="recipe" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="recipe" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>yijin</author>
-  </authors>
-  <commentList>
-    <comment ref="E2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>yijin:
-菜品ID、权重、最大出现次数</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>fixedDishes</t>
-  </si>
-  <si>
-    <t>requiredInitScore</t>
-  </si>
-  <si>
-    <t>*pool</t>
-  </si>
-  <si>
-    <t>##comment</t>
-  </si>
-  <si>
-    <t>菜谱ID</t>
-  </si>
-  <si>
-    <t>固定初始菜品ID列表，多个用 | 分隔</t>
-  </si>
-  <si>
-    <t>初始要求分</t>
-  </si>
-  <si>
-    <t>随机菜品池条目列表（dishId,weight,maxCount,initScore）</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>list,RecipeEntry</t>
-  </si>
-  <si>
-    <t>recipe_glutton</t>
-  </si>
-  <si>
-    <t>rice|rice</t>
-  </si>
-  <si>
-    <t>rice,150,0,5</t>
-  </si>
-  <si>
-    <t>egg,120,0,8</t>
-  </si>
-  <si>
-    <t>soup,100,0,9</t>
-  </si>
-  <si>
-    <t>noodle,90,0,12</t>
-  </si>
-  <si>
-    <t>feast,40,1,25</t>
-  </si>
-  <si>
-    <t>recipe_wok</t>
-  </si>
-  <si>
-    <t>egg</t>
-  </si>
-  <si>
-    <t>fish,100,0,15</t>
-  </si>
-  <si>
-    <t>dumpling,90,0,11</t>
-  </si>
-  <si>
-    <t>cake,60,2,20</t>
-  </si>
-  <si>
-    <t>recipe_chili</t>
-  </si>
-  <si>
-    <t>chili</t>
-  </si>
-  <si>
-    <t>chili,130,0,4</t>
-  </si>
-  <si>
-    <t>rice,120,0,5</t>
-  </si>
-  <si>
-    <t>soup,90,0,9</t>
-  </si>
-  <si>
-    <t>orange,80,0,10</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="21">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -619,153 +477,153 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -819,12 +677,91 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>yijin</author>
+  </authors>
+  <commentList>
+    <comment ref="E2" authorId="0" shapeId="0">
+      <text>
+        <t>yijin:
+菜品ID、权重、最大出现次数</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1110,164 +1047,276 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="22.7692307692308" customWidth="1"/>
-    <col min="4" max="4" width="17.8461538461538" customWidth="1"/>
-    <col min="5" max="5" width="22.4615384615385" customWidth="1"/>
+    <col width="13.0769230769231" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="22.7692307692308" customWidth="1" min="3" max="3"/>
+    <col width="17.8461538461538" customWidth="1" min="4" max="4"/>
+    <col width="22.4615384615385" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5">
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fixedDishes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>requiredInitScore</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>*pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>菜谱ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>固定初始菜品ID列表，多个用 | 分隔</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>初始要求分</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>随机菜品池条目列表（dishId,weight,maxCount,initScore）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>list,RecipeEntry</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>recipe_glutton</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>cookie</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="5:5">
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="5:5">
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="5:5">
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="5:5">
-      <c r="E8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5">
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>cookie,150,0,10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>macaron,120,0,8</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>daifuku,110,0,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>eggtart,110,0,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>jelly,100,0,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>sundae,60,2,20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>parfait,30,1,50</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>recipe_wok</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mochi</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>45</v>
       </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="5:5">
-      <c r="E10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="5:5">
-      <c r="E11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="5:5">
-      <c r="E12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5">
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>mochi,130,0,10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>gummy,110,0,8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>lollipop,100,0,10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>mousse,80,0,16</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>eggroll,60,2,30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>cream_cake,40,1,50</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>recipe_chili</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>pudding</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
       </c>
-      <c r="E13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="5:5">
-      <c r="E14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="5:5">
-      <c r="E15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="5:5">
-      <c r="E16" t="s">
-        <v>31</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>pudding,130,0,30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>choco_candy,120,0,10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>gold_choco,100,0,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>tanghulu,90,0,20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>choco_bar,60,1,40</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>marshmallow,30,1,80</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/GourmetProject/GameConfig/Datas/recipe.xlsx
+++ b/GourmetProject/GameConfig/Datas/recipe.xlsx
@@ -1198,7 +1198,6 @@
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>500</v>
       </c>

--- a/GourmetProject/GameConfig/Datas/recipe.xlsx
+++ b/GourmetProject/GameConfig/Datas/recipe.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15200"/>
+    <workbookView windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="recipe" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="92">
   <si>
     <t>##var</t>
   </si>
@@ -69,6 +69,12 @@
     <t>随机菜品池条目列表（dishId,weight,maxCount,initScore）</t>
   </si>
   <si>
+    <t>cookie</t>
+  </si>
+  <si>
+    <t>曲奇</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -81,88 +87,232 @@
     <t>list,RecipeEntry</t>
   </si>
   <si>
+    <t>macaron</t>
+  </si>
+  <si>
+    <t>马卡龙</t>
+  </si>
+  <si>
     <t>recipe_glutton</t>
   </si>
   <si>
     <t>cookie,10,2,10</t>
   </si>
   <si>
+    <t>pudding</t>
+  </si>
+  <si>
+    <t>布丁</t>
+  </si>
+  <si>
     <t>macaron,10,2,10</t>
   </si>
   <si>
+    <t>puff</t>
+  </si>
+  <si>
+    <t>泡芙</t>
+  </si>
+  <si>
     <t>daifuku,10,2,10</t>
   </si>
   <si>
+    <t>eggtart</t>
+  </si>
+  <si>
+    <t>蛋挞</t>
+  </si>
+  <si>
     <t>eggtart,10,2,10</t>
   </si>
   <si>
+    <t>mochi</t>
+  </si>
+  <si>
+    <t>麻薯</t>
+  </si>
+  <si>
     <t>jelly,10,2,10</t>
   </si>
   <si>
+    <t>daifuku</t>
+  </si>
+  <si>
+    <t>大福</t>
+  </si>
+  <si>
     <t>sundae,200,1,150</t>
   </si>
   <si>
+    <t>choco_candy</t>
+  </si>
+  <si>
+    <t>巧克力糖</t>
+  </si>
+  <si>
     <t>toffee,200,1,150</t>
   </si>
   <si>
+    <t>jelly</t>
+  </si>
+  <si>
+    <t>果冻</t>
+  </si>
+  <si>
     <t>cupcake,200,1,150</t>
   </si>
   <si>
+    <t>cream_cell</t>
+  </si>
+  <si>
+    <t>奶油小格</t>
+  </si>
+  <si>
     <t>eggroll,10000,1,300</t>
   </si>
   <si>
+    <t>sugarbean</t>
+  </si>
+  <si>
+    <t>糖豆</t>
+  </si>
+  <si>
     <t>choco_bar,10000,1,300</t>
   </si>
   <si>
+    <t>gold_choco</t>
+  </si>
+  <si>
+    <t>金巧克力</t>
+  </si>
+  <si>
     <t>eclair,10000,1,300</t>
   </si>
   <si>
+    <t>milk_slice</t>
+  </si>
+  <si>
+    <t>奶片</t>
+  </si>
+  <si>
     <t>recipe_wok</t>
   </si>
   <si>
-    <t>mochi</t>
-  </si>
-  <si>
     <t>mochi,130,0,10</t>
   </si>
   <si>
+    <t>sundae</t>
+  </si>
+  <si>
+    <t>圣代</t>
+  </si>
+  <si>
     <t>gummy,110,0,8</t>
   </si>
   <si>
+    <t>cone</t>
+  </si>
+  <si>
+    <t>甜筒</t>
+  </si>
+  <si>
     <t>lollipop,100,0,10</t>
   </si>
   <si>
+    <t>lollipop</t>
+  </si>
+  <si>
+    <t>棒棒糖</t>
+  </si>
+  <si>
     <t>mousse,80,0,16</t>
   </si>
   <si>
+    <t>gummy</t>
+  </si>
+  <si>
+    <t>软糖</t>
+  </si>
+  <si>
     <t>eggroll,60,2,30</t>
   </si>
   <si>
+    <t>cupcake</t>
+  </si>
+  <si>
+    <t>糖霜蛋糕</t>
+  </si>
+  <si>
     <t>cream_cake,40,1,50</t>
   </si>
   <si>
+    <t>mousse</t>
+  </si>
+  <si>
+    <t>慕斯蛋糕</t>
+  </si>
+  <si>
     <t>recipe_chili</t>
   </si>
   <si>
-    <t>pudding</t>
-  </si>
-  <si>
     <t>pudding,130,0,30</t>
   </si>
   <si>
+    <t>toffee</t>
+  </si>
+  <si>
+    <t>太妃糖</t>
+  </si>
+  <si>
     <t>choco_candy,120,0,10</t>
   </si>
   <si>
+    <t>nougat</t>
+  </si>
+  <si>
+    <t>牛轧糖</t>
+  </si>
+  <si>
     <t>gold_choco,100,0,6</t>
   </si>
   <si>
+    <t>eggroll</t>
+  </si>
+  <si>
+    <t>蛋卷</t>
+  </si>
+  <si>
     <t>tanghulu,90,0,20</t>
   </si>
   <si>
+    <t>choco_bar</t>
+  </si>
+  <si>
+    <t>巧克力棒</t>
+  </si>
+  <si>
     <t>choco_bar,60,1,40</t>
   </si>
   <si>
+    <t>eclair</t>
+  </si>
+  <si>
+    <t>闪电泡芙</t>
+  </si>
+  <si>
     <t>marshmallow,30,1,80</t>
+  </si>
+  <si>
+    <t>2*4</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>z</t>
   </si>
 </sst>
 </file>
@@ -175,13 +325,24 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -333,12 +494,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -651,140 +818,155 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1132,15 +1314,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <dimension ref="A1:V36"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="1" customWidth="1"/>
     <col min="3" max="3" width="15.1538461538462" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.8461538461538" style="1" customWidth="1"/>
     <col min="5" max="5" width="60.6923076923077" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="6" max="8" width="9" style="1"/>
+    <col min="9" max="9" width="13.4615384615385" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9" style="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1160,7 +1345,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:21">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1176,161 +1361,776 @@
       <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="1">
+        <f>VLOOKUP(H2,$R$4:$T$6,3,FALSE)</f>
+        <v>40</v>
+      </c>
+      <c r="K2" s="6">
+        <v>2</v>
+      </c>
+      <c r="L2" s="4">
+        <v>10</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="3">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="1">
+        <f t="shared" ref="J3:J25" si="0">VLOOKUP(H3,$R$4:$T$6,3,FALSE)</f>
+        <v>70</v>
+      </c>
+      <c r="K3" s="6">
+        <v>2</v>
+      </c>
+      <c r="L3" s="4">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5">
+      <c r="U3" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="2:21">
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="5:5">
+        <v>19</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="1">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="K4" s="6">
+        <v>2</v>
+      </c>
+      <c r="L4" s="4">
+        <v>10</v>
+      </c>
+      <c r="R4" s="1">
+        <v>1</v>
+      </c>
+      <c r="S4" s="1">
+        <v>7</v>
+      </c>
+      <c r="T4" s="1">
+        <v>40</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="5:21">
       <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="5:5">
+        <v>22</v>
+      </c>
+      <c r="H5" s="3">
+        <v>3</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="1">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="K5" s="6">
+        <v>2</v>
+      </c>
+      <c r="L5" s="4">
+        <v>10</v>
+      </c>
+      <c r="R5" s="1">
+        <v>2</v>
+      </c>
+      <c r="S5" s="1">
+        <v>3</v>
+      </c>
+      <c r="T5" s="1">
+        <v>70</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="5:21">
       <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="5:5">
+        <v>25</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="1">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="K6" s="6">
+        <v>2</v>
+      </c>
+      <c r="L6" s="4">
+        <v>10</v>
+      </c>
+      <c r="R6" s="1">
+        <v>3</v>
+      </c>
+      <c r="S6" s="1">
+        <v>3</v>
+      </c>
+      <c r="T6" s="1">
+        <v>70</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="5:21">
       <c r="E7" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="5:5">
+        <v>28</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="1">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="K7" s="6">
+        <v>2</v>
+      </c>
+      <c r="L7" s="4">
+        <v>10</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="5:21">
       <c r="E8" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="5:5">
+        <v>31</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="1">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="K8" s="6">
+        <v>2</v>
+      </c>
+      <c r="L8" s="4">
+        <v>10</v>
+      </c>
+      <c r="R8" s="1">
+        <v>1</v>
+      </c>
+      <c r="S8" s="1">
+        <v>1</v>
+      </c>
+      <c r="T8" s="1">
+        <v>60</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="5:21">
       <c r="E9" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="5:5">
+        <v>34</v>
+      </c>
+      <c r="H9" s="3">
+        <v>2</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="K9" s="6">
+        <v>2</v>
+      </c>
+      <c r="L9" s="4">
+        <v>10</v>
+      </c>
+      <c r="R9" s="1">
+        <v>2</v>
+      </c>
+      <c r="S9" s="1">
+        <v>4</v>
+      </c>
+      <c r="T9" s="1">
+        <v>30</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="5:21">
       <c r="E10" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="5:5">
+        <v>37</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J10" s="1">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="K10" s="6">
+        <v>2</v>
+      </c>
+      <c r="L10" s="4">
+        <v>10</v>
+      </c>
+      <c r="R10" s="1">
+        <v>3</v>
+      </c>
+      <c r="S10" s="1">
+        <v>3</v>
+      </c>
+      <c r="T10" s="1">
+        <v>40</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="5:21">
       <c r="E11" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="5:5">
+        <v>40</v>
+      </c>
+      <c r="H11" s="4">
+        <v>3</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" s="1">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="K11" s="6">
+        <v>2</v>
+      </c>
+      <c r="L11" s="4">
+        <v>10</v>
+      </c>
+      <c r="U11" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="5:21">
       <c r="E12" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="5:5">
+        <v>43</v>
+      </c>
+      <c r="H12" s="3">
+        <v>2</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J12" s="1">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="K12" s="6">
+        <v>2</v>
+      </c>
+      <c r="L12" s="4">
+        <v>10</v>
+      </c>
+      <c r="U12" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="5:21">
       <c r="E13" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="5:5">
+        <v>46</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J13" s="1">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="K13" s="6">
+        <v>2</v>
+      </c>
+      <c r="L13" s="4">
+        <v>10</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="5:21">
       <c r="E14" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5">
+        <v>49</v>
+      </c>
+      <c r="H14" s="3">
+        <v>3</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J14" s="1">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="K14" s="6">
+        <v>2</v>
+      </c>
+      <c r="L14" s="4">
+        <v>10</v>
+      </c>
+      <c r="U14" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="2:21">
       <c r="B15" s="1" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D15" s="1">
         <v>45</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="5:5">
+        <v>53</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J15" s="1">
+        <f>VLOOKUP(H15,$R$8:$T$10,3,FALSE)</f>
+        <v>60</v>
+      </c>
+      <c r="K15" s="6">
+        <v>2</v>
+      </c>
+      <c r="L15" s="4">
+        <v>20</v>
+      </c>
+      <c r="U15" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="5:21">
       <c r="E16" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="5:5">
+        <v>56</v>
+      </c>
+      <c r="H16" s="3">
+        <v>3</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="J16" s="1">
+        <f t="shared" ref="J16:J22" si="1">VLOOKUP(H16,$R$8:$T$10,3,FALSE)</f>
+        <v>40</v>
+      </c>
+      <c r="K16" s="6">
+        <v>2</v>
+      </c>
+      <c r="L16" s="4">
+        <v>20</v>
+      </c>
+      <c r="U16" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="5:21">
       <c r="E17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H17" s="3">
+        <v>2</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J17" s="1">
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="18" spans="5:5">
+      <c r="K17" s="6">
+        <v>2</v>
+      </c>
+      <c r="L17" s="4">
+        <v>20</v>
+      </c>
+      <c r="U17" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="5:21">
       <c r="E18" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="5:5">
+        <v>62</v>
+      </c>
+      <c r="H18" s="3">
+        <v>2</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="J18" s="1">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="K18" s="6">
+        <v>2</v>
+      </c>
+      <c r="L18" s="4">
+        <v>20</v>
+      </c>
+      <c r="N18" s="1">
+        <v>300</v>
+      </c>
+      <c r="U18" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="5:21">
       <c r="E19" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="5:5">
+        <v>65</v>
+      </c>
+      <c r="H19" s="3">
+        <v>3</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J19" s="1">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="K19" s="6">
+        <v>2</v>
+      </c>
+      <c r="L19" s="4">
+        <v>20</v>
+      </c>
+      <c r="U19" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="5:21">
       <c r="E20" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5">
+        <v>68</v>
+      </c>
+      <c r="H20" s="3">
+        <v>3</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J20" s="1">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="K20" s="6">
+        <v>2</v>
+      </c>
+      <c r="L20" s="4">
+        <v>20</v>
+      </c>
+      <c r="N20" s="1">
+        <v>150</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21">
       <c r="B21" s="1" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D21" s="1">
         <v>38</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="5:5">
+        <v>72</v>
+      </c>
+      <c r="H21" s="3">
+        <v>2</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J21" s="1">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="K21" s="6">
+        <v>2</v>
+      </c>
+      <c r="L21" s="4">
+        <v>20</v>
+      </c>
+      <c r="U21" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="5:21">
       <c r="E22" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="5:5">
+        <v>75</v>
+      </c>
+      <c r="H22" s="3">
+        <v>2</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="J22" s="1">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="K22" s="6">
+        <v>2</v>
+      </c>
+      <c r="L22" s="4">
+        <v>20</v>
+      </c>
+      <c r="U22" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="5:21">
       <c r="E23" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="5:5">
+        <v>78</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="J23" s="1">
+        <v>50</v>
+      </c>
+      <c r="K23" s="6">
+        <v>1</v>
+      </c>
+      <c r="L23" s="4">
+        <v>30</v>
+      </c>
+      <c r="U23" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="5:21">
       <c r="E24" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="5:5">
+        <v>81</v>
+      </c>
+      <c r="H24" s="3">
+        <v>2</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J24" s="1">
+        <v>50</v>
+      </c>
+      <c r="K24" s="6">
+        <v>1</v>
+      </c>
+      <c r="L24" s="4">
+        <v>30</v>
+      </c>
+      <c r="U24" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="5:21">
       <c r="E25" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="5:5">
+        <v>84</v>
+      </c>
+      <c r="H25" s="3">
+        <v>3</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J25" s="1">
+        <v>50</v>
+      </c>
+      <c r="K25" s="6">
+        <v>1</v>
+      </c>
+      <c r="L25" s="4">
+        <v>30</v>
+      </c>
+      <c r="U25" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="5:22">
       <c r="E26" s="1" t="s">
-        <v>41</v>
+        <v>87</v>
+      </c>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="U26" s="4"/>
+      <c r="V26" s="4"/>
+    </row>
+    <row r="28" spans="14:14">
+      <c r="N28" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="8:8">
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31" spans="8:8">
+      <c r="H31" s="4"/>
+    </row>
+    <row r="32" spans="12:19">
+      <c r="L32" s="1">
+        <v>1</v>
+      </c>
+      <c r="M32">
+        <v>3</v>
+      </c>
+      <c r="N32" s="1">
+        <v>4</v>
+      </c>
+      <c r="O32" s="1">
+        <v>5</v>
+      </c>
+      <c r="P32" s="1">
+        <v>4</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="S32" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="12:19">
+      <c r="L33" s="1">
+        <v>2</v>
+      </c>
+      <c r="M33">
+        <v>2</v>
+      </c>
+      <c r="N33" s="1">
+        <v>0</v>
+      </c>
+      <c r="O33" s="1">
+        <v>1</v>
+      </c>
+      <c r="P33" s="1">
+        <v>3</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="S33" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="12:19">
+      <c r="L34" s="1">
+        <v>3</v>
+      </c>
+      <c r="M34">
+        <v>1</v>
+      </c>
+      <c r="N34" s="1">
+        <v>2</v>
+      </c>
+      <c r="O34" s="1">
+        <v>1</v>
+      </c>
+      <c r="P34" s="1">
+        <v>0</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="S34" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="13:16">
+      <c r="M36">
+        <f>SUMPRODUCT($L$32:$L$34,M32:M34)</f>
+        <v>10</v>
+      </c>
+      <c r="N36">
+        <f>SUMPRODUCT($L$32:$L$34,N32:N34)</f>
+        <v>10</v>
+      </c>
+      <c r="O36">
+        <f>SUMPRODUCT($L$32:$L$34,O32:O34)</f>
+        <v>10</v>
+      </c>
+      <c r="P36">
+        <f>SUMPRODUCT($L$32:$L$34,P32:P34)</f>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/recipe.xlsx
+++ b/GourmetProject/GameConfig/Datas/recipe.xlsx
@@ -62,13 +62,13 @@
     <t>recipe_glutton_group_1|recipe_glutton_group_2|recipe_glutton_group_3</t>
   </si>
   <si>
-    <t>4,0,2;10</t>
-  </si>
-  <si>
-    <t>3,2,1;30</t>
-  </si>
-  <si>
-    <t>3,3,0;10</t>
+    <t>7,0,2;10</t>
+  </si>
+  <si>
+    <t>6,2,1;30</t>
+  </si>
+  <si>
+    <t>7,3,0;10</t>
   </si>
   <si>
     <t>recipe_wok</t>
@@ -1406,7 +1406,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -1546,7 +1546,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="7:9">
+    <row r="29" spans="12:12">
+      <c r="L29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="7:12">
       <c r="G30">
         <v>2</v>
       </c>
@@ -1555,6 +1560,9 @@
       </c>
       <c r="I30">
         <v>2</v>
+      </c>
+      <c r="L30">
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="7:10">
@@ -1582,42 +1590,76 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="7:7">
+    <row r="33" spans="7:9">
       <c r="G33">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="8:9">
-      <c r="H36">
+      <c r="H33">
+        <v>2</v>
+      </c>
+      <c r="I33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="7:9">
+      <c r="G34">
+        <v>2</v>
+      </c>
+      <c r="H34">
+        <v>2</v>
+      </c>
+      <c r="I34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="7:9">
+      <c r="G35">
+        <v>2</v>
+      </c>
+      <c r="H35">
+        <v>2</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="7:9">
+      <c r="G36">
         <v>2</v>
       </c>
       <c r="I36">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="8:9">
-      <c r="H37">
-        <v>2</v>
-      </c>
-      <c r="I37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="9:9">
-      <c r="I38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="7:8">
-      <c r="G39">
+    <row r="39" spans="8:9">
+      <c r="H39">
+        <v>2</v>
+      </c>
+      <c r="I39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="8:9">
+      <c r="H40">
+        <v>2</v>
+      </c>
+      <c r="I40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="7:9">
+      <c r="G41">
         <v>3</v>
       </c>
-      <c r="H39">
+      <c r="I41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="7:8">
+      <c r="G42">
         <v>3</v>
       </c>
-    </row>
-    <row r="40" spans="7:7">
-      <c r="G40">
+      <c r="H42">
         <v>3</v>
       </c>
     </row>
@@ -1694,7 +1736,7 @@
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7" t="str">
-        <f t="shared" ref="C5:C27" si="0">_xlfn.TEXTJOIN(",",TRUE,F5:H5)</f>
+        <f t="shared" ref="C5:C28" si="0">_xlfn.TEXTJOIN(",",TRUE,F5:H5)</f>
         <v>arrow_cookie_2,1,2</v>
       </c>
       <c r="F5" s="8" t="s">
@@ -2072,7 +2114,7 @@
     </row>
     <row r="28" spans="3:8">
       <c r="C28" s="7" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,F28:H28)</f>
+        <f t="shared" si="0"/>
         <v>palmier,1,1</v>
       </c>
       <c r="F28" s="8" t="s">

--- a/GourmetProject/GameConfig/Datas/recipe.xlsx
+++ b/GourmetProject/GameConfig/Datas/recipe.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15300"/>
+    <workbookView windowHeight="15280"/>
   </bookViews>
   <sheets>
     <sheet name="recipe" sheetId="1" r:id="rId1"/>
@@ -62,13 +62,13 @@
     <t>recipe_glutton_group_1|recipe_glutton_group_2|recipe_glutton_group_3</t>
   </si>
   <si>
-    <t>7,0,2;10</t>
-  </si>
-  <si>
-    <t>6,2,1;30</t>
-  </si>
-  <si>
-    <t>7,3,0;10</t>
+    <t>12,0,2;10</t>
+  </si>
+  <si>
+    <t>12,2,1;30</t>
+  </si>
+  <si>
+    <t>12,3,0;10</t>
   </si>
   <si>
     <t>recipe_wok</t>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="C4" s="7" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,F4:H4)</f>
-        <v>arrow_cookie_1,1,2</v>
+        <v>arrow_cookie_1,1,3</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>31</v>
@@ -1729,7 +1729,7 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1737,7 +1737,7 @@
       <c r="B5" s="7"/>
       <c r="C5" s="7" t="str">
         <f t="shared" ref="C5:C28" si="0">_xlfn.TEXTJOIN(",",TRUE,F5:H5)</f>
-        <v>arrow_cookie_2,1,2</v>
+        <v>arrow_cookie_2,1,3</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>32</v>
@@ -1746,7 +1746,7 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1754,7 +1754,7 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>arrow_cookie_3,1,2</v>
+        <v>arrow_cookie_3,1,3</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>33</v>
@@ -1763,7 +1763,7 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1771,7 +1771,7 @@
       <c r="B7" s="7"/>
       <c r="C7" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>arrow_cookie_4,1,2</v>
+        <v>arrow_cookie_4,1,3</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>34</v>
@@ -1780,7 +1780,7 @@
         <v>1</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:8">

--- a/GourmetProject/GameConfig/Datas/recipe.xlsx
+++ b/GourmetProject/GameConfig/Datas/recipe.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15280"/>
+    <workbookView windowHeight="15280" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="recipe" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="69">
   <si>
     <t>##var</t>
   </si>
@@ -134,94 +134,76 @@
     <t>eggtart</t>
   </si>
   <si>
+    <t>recipe_glutton_group_3</t>
+  </si>
+  <si>
     <t>sugarbean</t>
   </si>
   <si>
-    <t>cheesecake</t>
-  </si>
-  <si>
-    <t>mousse</t>
-  </si>
-  <si>
-    <t>fruit_candy</t>
-  </si>
-  <si>
-    <t>choco_bar</t>
-  </si>
-  <si>
-    <t>cup_cake</t>
-  </si>
-  <si>
-    <t>cream</t>
-  </si>
-  <si>
-    <t>recipe_glutton_group_3</t>
-  </si>
-  <si>
     <t>eggroll</t>
   </si>
   <si>
     <t>baguette</t>
   </si>
   <si>
+    <t>recipe_wok_group_1</t>
+  </si>
+  <si>
+    <t>mochi,40,2</t>
+  </si>
+  <si>
     <t>tanghulu</t>
   </si>
   <si>
+    <t>eggroll,50,1</t>
+  </si>
+  <si>
     <t>cake_slice</t>
   </si>
   <si>
+    <t>recipe_wok_group_2</t>
+  </si>
+  <si>
+    <t>gummy,30,2</t>
+  </si>
+  <si>
     <t>long_cake</t>
   </si>
   <si>
+    <t>lollipop,30,2</t>
+  </si>
+  <si>
     <t>eclair</t>
   </si>
   <si>
+    <t>recipe_wok_group_3</t>
+  </si>
+  <si>
+    <t>mousse,40,2</t>
+  </si>
+  <si>
     <t>gummy</t>
   </si>
   <si>
+    <t>cream_cake,40,1</t>
+  </si>
+  <si>
     <t>chocolate_strip</t>
   </si>
   <si>
+    <t>recipe_chili_group_1</t>
+  </si>
+  <si>
+    <t>pudding,40,2</t>
+  </si>
+  <si>
     <t>cake_roll</t>
   </si>
   <si>
+    <t>gold_choco,40,2</t>
+  </si>
+  <si>
     <t>palmier</t>
-  </si>
-  <si>
-    <t>recipe_wok_group_1</t>
-  </si>
-  <si>
-    <t>mochi,40,2</t>
-  </si>
-  <si>
-    <t>eggroll,50,1</t>
-  </si>
-  <si>
-    <t>recipe_wok_group_2</t>
-  </si>
-  <si>
-    <t>gummy,30,2</t>
-  </si>
-  <si>
-    <t>lollipop,30,2</t>
-  </si>
-  <si>
-    <t>recipe_wok_group_3</t>
-  </si>
-  <si>
-    <t>mousse,40,2</t>
-  </si>
-  <si>
-    <t>cream_cake,40,1</t>
-  </si>
-  <si>
-    <t>recipe_chili_group_1</t>
-  </si>
-  <si>
-    <t>pudding,40,2</t>
-  </si>
-  <si>
-    <t>gold_choco,40,2</t>
   </si>
   <si>
     <t>recipe_chili_group_2</t>
@@ -1672,7 +1654,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -1736,7 +1718,7 @@
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7" t="str">
-        <f t="shared" ref="C5:C28" si="0">_xlfn.TEXTJOIN(",",TRUE,F5:H5)</f>
+        <f>_xlfn.TEXTJOIN(",",TRUE,F5:H5)</f>
         <v>arrow_cookie_2,1,3</v>
       </c>
       <c r="F5" s="8" t="s">
@@ -1753,7 +1735,7 @@
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(",",TRUE,F6:H6)</f>
         <v>arrow_cookie_3,1,3</v>
       </c>
       <c r="F6" s="8" t="s">
@@ -1770,7 +1752,7 @@
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(",",TRUE,F7:H7)</f>
         <v>arrow_cookie_4,1,3</v>
       </c>
       <c r="F7" s="8" t="s">
@@ -1789,7 +1771,7 @@
         <v>35</v>
       </c>
       <c r="C8" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(",",TRUE,F8:H8)</f>
         <v>jelly,1,1</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -1806,8 +1788,8 @@
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>cupcake,1,1</v>
+        <f>_xlfn.TEXTJOIN(",",TRUE,F10:H10)</f>
+        <v>eggtart,1,1</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>37</v>
@@ -1822,8 +1804,8 @@
     <row r="10" spans="1:8">
       <c r="A10" s="7"/>
       <c r="C10" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>eggtart,1,1</v>
+        <f>_xlfn.TEXTJOIN(",",TRUE,F11:H11)</f>
+        <v>sugarbean,1,1</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>38</v>
@@ -1837,13 +1819,15 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
+      <c r="B11" s="7" t="s">
+        <v>39</v>
+      </c>
       <c r="C11" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>sugarbean,1,1</v>
+        <f>_xlfn.TEXTJOIN(",",TRUE,F17:H17)</f>
+        <v>eclair,1,1</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1854,13 +1838,12 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
       <c r="C12" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>cheesecake,1,1</v>
+        <f>_xlfn.TEXTJOIN(",",TRUE,F18:H18)</f>
+        <v>gummy,1,1</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1872,11 +1855,11 @@
     <row r="13" spans="1:8">
       <c r="A13" s="7"/>
       <c r="C13" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>mousse,1,1</v>
+        <f>_xlfn.TEXTJOIN(",",TRUE,F20:H20)</f>
+        <v>cake_roll,1,1</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1887,13 +1870,14 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>fruit_candy,1,1</v>
+      <c r="B14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1904,12 +1888,12 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="7"/>
-      <c r="C15" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>choco_bar,1,1</v>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1920,12 +1904,14 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="7"/>
-      <c r="C16" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>mochi,1,1</v>
+      <c r="B16" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1936,12 +1922,12 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="7"/>
-      <c r="C17" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>cup_cake,1,1</v>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1952,12 +1938,14 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="7"/>
-      <c r="C18" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>cream,1,1</v>
+      <c r="B18" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1968,15 +1956,12 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="7"/>
-      <c r="B19" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>eggroll,1,1</v>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1985,14 +1970,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="7"/>
-      <c r="C20" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>baguette,1,1</v>
+    <row r="20" spans="2:8">
+      <c r="B20" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -2001,14 +1987,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="7"/>
-      <c r="C21" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>tanghulu,1,1</v>
+    <row r="21" spans="2:8">
+      <c r="B21" s="7"/>
+      <c r="C21" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -2017,199 +2002,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="7"/>
-      <c r="C22" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>cake_slice,1,1</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="7"/>
-      <c r="C23" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>long_cake,1,1</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-      <c r="H23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="7"/>
-      <c r="C24" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>eclair,1,1</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="7"/>
-      <c r="C25" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>gummy,1,1</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="7"/>
-      <c r="C26" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>chocolate_strip,1,1</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="3:8">
-      <c r="C27" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>cake_roll,1,1</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="3:8">
-      <c r="C28" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>palmier,1,1</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-      <c r="H28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6">
-      <c r="B29" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F29" s="8"/>
-    </row>
-    <row r="30" spans="2:3">
-      <c r="B30" s="7"/>
-      <c r="C30" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3">
-      <c r="B31" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3">
-      <c r="B32" s="7"/>
-      <c r="C32" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3">
-      <c r="B33" s="7" t="s">
+    <row r="22" spans="2:6">
+      <c r="B22" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C22" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="34" spans="2:3">
-      <c r="B34" s="7"/>
-      <c r="C34" s="7" t="s">
+      <c r="F22" s="8"/>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23" s="7"/>
+      <c r="C23" s="7" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="35" spans="2:3">
-      <c r="B35" s="7" t="s">
+    <row r="24" spans="2:3">
+      <c r="B24" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C24" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="2:3">
-      <c r="B36" s="7"/>
-      <c r="C36" s="7" t="s">
+    <row r="25" spans="2:3">
+      <c r="B25" s="7"/>
+      <c r="C25" s="7" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3">
-      <c r="B37" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3">
-      <c r="B38" s="7"/>
-      <c r="C38" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3">
-      <c r="B39" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3">
-      <c r="B40" s="7"/>
-      <c r="C40" s="7" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
